--- a/output/pdf_financials_xlsx/COS.xlsx
+++ b/output/pdf_financials_xlsx/COS.xlsx
@@ -747,10 +747,10 @@
         <v>-0.44047</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="17">
@@ -843,10 +843,10 @@
         <v>-0.44047</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="21">
@@ -906,10 +906,10 @@
         <v>-0.44047</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="24">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>27.028312</v>
+        <v>-27.028312</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>32.966967</v>
+        <v>-32.966967</v>
       </c>
     </row>
     <row r="27">
@@ -996,10 +996,10 @@
         <v>-0.44047</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="28">
@@ -1038,10 +1038,10 @@
         <v>-0.44047</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="30">
@@ -1086,10 +1086,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>2.162265</v>
+        <v>-2.162265</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.989009</v>
+        <v>-0.989009</v>
       </c>
     </row>
     <row r="92">

--- a/output/pdf_financials_xlsx/COS.xlsx
+++ b/output/pdf_financials_xlsx/COS.xlsx
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009625999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001069</v>
       </c>
     </row>
     <row r="35">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009625999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001069</v>
       </c>
     </row>
     <row r="37">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
